--- a/Community Engagement Rankings 2026-04.xlsx
+++ b/Community Engagement Rankings 2026-04.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D336"/>
+  <dimension ref="A1:D344"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -419,13 +419,13 @@
         <v>peacegrappler_mma</v>
       </c>
       <c r="B2">
-        <v>1170</v>
+        <v>1240</v>
       </c>
       <c r="C2">
         <v>3</v>
       </c>
       <c r="D2">
-        <v>927</v>
+        <v>996</v>
       </c>
     </row>
     <row r="3">
@@ -433,13 +433,13 @@
         <v>quemuel_ottoni</v>
       </c>
       <c r="B3">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="C3">
         <v>10</v>
       </c>
       <c r="D3">
-        <v>279</v>
+        <v>280</v>
       </c>
     </row>
     <row r="4">
@@ -447,13 +447,13 @@
         <v>luis_pequeno_mma</v>
       </c>
       <c r="B4">
-        <v>317</v>
+        <v>327</v>
       </c>
       <c r="C4">
         <v>26</v>
       </c>
       <c r="D4">
-        <v>32</v>
+        <v>41</v>
       </c>
     </row>
     <row r="5">
@@ -461,13 +461,13 @@
         <v>enzocardoso.bjj</v>
       </c>
       <c r="B5">
-        <v>194</v>
+        <v>207</v>
       </c>
       <c r="C5">
         <v>9</v>
       </c>
       <c r="D5">
-        <v>70</v>
+        <v>73</v>
       </c>
     </row>
     <row r="6">
@@ -475,13 +475,13 @@
         <v>pedr00jj</v>
       </c>
       <c r="B6">
-        <v>132</v>
+        <v>145</v>
       </c>
       <c r="C6">
         <v>4</v>
       </c>
       <c r="D6">
-        <v>61</v>
+        <v>65</v>
       </c>
     </row>
     <row r="7">
@@ -489,13 +489,13 @@
         <v>pablofiorindi</v>
       </c>
       <c r="B7">
-        <v>130</v>
+        <v>142</v>
       </c>
       <c r="C7">
         <v>7</v>
       </c>
       <c r="D7">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="8">
@@ -503,10 +503,10 @@
         <v>rpsantos_mma</v>
       </c>
       <c r="B8">
-        <v>141</v>
+        <v>155</v>
       </c>
       <c r="C8">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D8">
         <v>46</v>
@@ -514,86 +514,86 @@
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>pg_grappling</v>
+        <v>rm.nicki</v>
       </c>
       <c r="B9">
-        <v>91</v>
+        <v>78</v>
       </c>
       <c r="C9">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D9">
-        <v>38</v>
+        <v>73</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>rm.nicki</v>
+        <v>pg_grappling</v>
       </c>
       <c r="B10">
-        <v>74</v>
+        <v>91</v>
       </c>
       <c r="C10">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D10">
-        <v>69</v>
+        <v>38</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>anaaj_camargo</v>
+        <v>hugo7jj</v>
       </c>
       <c r="B11">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="C11">
         <v>0</v>
       </c>
       <c r="D11">
-        <v>45</v>
+        <v>41</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>hugo7jj</v>
+        <v>anaaj_camargo</v>
       </c>
       <c r="B12">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="C12">
         <v>0</v>
       </c>
       <c r="D12">
-        <v>41</v>
+        <v>45</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>ryangandraufc</v>
+        <v>irmandadefightteam</v>
       </c>
       <c r="B13">
-        <v>39</v>
+        <v>54</v>
       </c>
       <c r="C13">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="D13">
-        <v>34</v>
+        <v>4</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>irmandadefightteam</v>
+        <v>ryangandraufc</v>
       </c>
       <c r="B14">
-        <v>52</v>
+        <v>39</v>
       </c>
       <c r="C14">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="D14">
-        <v>2</v>
+        <v>36</v>
       </c>
     </row>
     <row r="15">
@@ -682,44 +682,44 @@
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>cleyton_jesuss</v>
+        <v>aline.r15</v>
       </c>
       <c r="B21">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C21">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D21">
-        <v>18</v>
+        <v>7</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>god.motivacao</v>
+        <v>cleyton_jesuss</v>
       </c>
       <c r="B22">
-        <v>7</v>
+        <v>23</v>
       </c>
       <c r="C22">
-        <v>117</v>
+        <v>4</v>
       </c>
       <c r="D22">
-        <v>34</v>
+        <v>18</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>aline.r15</v>
+        <v>god.motivacao</v>
       </c>
       <c r="B23">
-        <v>22</v>
+        <v>8</v>
       </c>
       <c r="C23">
-        <v>6</v>
+        <v>117</v>
       </c>
       <c r="D23">
-        <v>5</v>
+        <v>34</v>
       </c>
     </row>
     <row r="24">
@@ -794,13 +794,13 @@
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>eliassilverio</v>
+        <v>pedromadeira.s</v>
       </c>
       <c r="B29">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="C29">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="D29">
         <v>6</v>
@@ -808,16 +808,16 @@
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>pedromadeira.s</v>
+        <v>eliassilverio</v>
       </c>
       <c r="B30">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C30">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="D30">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="31">
@@ -867,7 +867,7 @@
         <v>maxgandra</v>
       </c>
       <c r="B34">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C34">
         <v>2</v>
@@ -1130,27 +1130,27 @@
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>marcelogabrielmma</v>
+        <v>excelentfightcompetition</v>
       </c>
       <c r="B53">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C53">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D53">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>_oliveira09_</v>
+        <v>marcelogabrielmma</v>
       </c>
       <c r="B54">
         <v>3</v>
       </c>
       <c r="C54">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D54">
         <v>3</v>
@@ -1158,97 +1158,97 @@
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>edebetim_</v>
+        <v>_oliveira09_</v>
       </c>
       <c r="B55">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C55">
+        <v>4</v>
+      </c>
+      <c r="D55">
         <v>3</v>
-      </c>
-      <c r="D55">
-        <v>5</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>gabrielsouzamma</v>
+        <v>edebetim_</v>
       </c>
       <c r="B56">
         <v>2</v>
       </c>
       <c r="C56">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D56">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>salost.ofc</v>
+        <v>gabrielsouzamma</v>
       </c>
       <c r="B57">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C57">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D57">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>alfredo_miras</v>
+        <v>salost.ofc</v>
       </c>
       <c r="B58">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C58">
         <v>0</v>
       </c>
       <c r="D58">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>ravenrodriguez___</v>
+        <v>alfredo_miras</v>
       </c>
       <c r="B59">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C59">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D59">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>fabinho_falcao_</v>
+        <v>ravenrodriguez___</v>
       </c>
       <c r="B60">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C60">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D60">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>ailinperezufc</v>
+        <v>fabinho_falcao_</v>
       </c>
       <c r="B61">
         <v>2</v>
       </c>
       <c r="C61">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D61">
         <v>1</v>
@@ -1256,16 +1256,16 @@
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>mah__vergueiro</v>
+        <v>ailinperezufc</v>
       </c>
       <c r="B62">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C62">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D62">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="63">
@@ -1276,7 +1276,7 @@
         <v>2</v>
       </c>
       <c r="C63">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D63">
         <v>2</v>
@@ -1284,10 +1284,10 @@
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>lipe.ftt</v>
+        <v>mah__vergueiro</v>
       </c>
       <c r="B64">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C64">
         <v>0</v>
@@ -1298,7 +1298,7 @@
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>fau_gfs</v>
+        <v>lipe.ftt</v>
       </c>
       <c r="B65">
         <v>4</v>
@@ -1312,21 +1312,21 @@
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>ninjatheorist</v>
+        <v>fau_gfs</v>
       </c>
       <c r="B66">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C66">
         <v>0</v>
       </c>
       <c r="D66">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>shawlin13oficial</v>
+        <v>ninjatheorist</v>
       </c>
       <c r="B67">
         <v>2</v>
@@ -1335,12 +1335,12 @@
         <v>0</v>
       </c>
       <c r="D67">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>eduardorodrigrs</v>
+        <v>shawlin13oficial</v>
       </c>
       <c r="B68">
         <v>2</v>
@@ -1354,7 +1354,7 @@
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>diego.dieguito.3914</v>
+        <v>eduardorodrigrs</v>
       </c>
       <c r="B69">
         <v>2</v>
@@ -1368,7 +1368,7 @@
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>febrancatti</v>
+        <v>diego.dieguito.3914</v>
       </c>
       <c r="B70">
         <v>2</v>
@@ -1382,13 +1382,13 @@
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>dogodoyfoto</v>
+        <v>febrancatti</v>
       </c>
       <c r="B71">
         <v>2</v>
       </c>
       <c r="C71">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D71">
         <v>1</v>
@@ -1396,35 +1396,35 @@
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>reifernandes</v>
+        <v>dogodoyfoto</v>
       </c>
       <c r="B72">
         <v>2</v>
       </c>
       <c r="C72">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D72">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>daniel_dias_214</v>
+        <v>reifernandes</v>
       </c>
       <c r="B73">
         <v>2</v>
       </c>
       <c r="C73">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D73">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>fabiomarcelinopersonal</v>
+        <v>daniel_dias_214</v>
       </c>
       <c r="B74">
         <v>2</v>
@@ -1438,27 +1438,27 @@
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>alexsandra_kairos</v>
+        <v>fabiomarcelinopersonal</v>
       </c>
       <c r="B75">
         <v>2</v>
       </c>
       <c r="C75">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D75">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>f.luan_11</v>
+        <v>alexsandra_kairos</v>
       </c>
       <c r="B76">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C76">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D76">
         <v>0</v>
@@ -1466,21 +1466,21 @@
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>vitorpetrino</v>
+        <v>f.luan_11</v>
       </c>
       <c r="B77">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C77">
         <v>0</v>
       </c>
       <c r="D77">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>jcchagas_</v>
+        <v>vitorpetrino</v>
       </c>
       <c r="B78">
         <v>2</v>
@@ -1494,91 +1494,91 @@
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>anderson.logan.35</v>
+        <v>jcchagas_</v>
       </c>
       <c r="B79">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C79">
         <v>0</v>
       </c>
       <c r="D79">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>marifferreirac</v>
+        <v>anderson.logan.35</v>
       </c>
       <c r="B80">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C80">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D80">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>odeivisoncardoso</v>
+        <v>marifferreirac</v>
       </c>
       <c r="B81">
         <v>1</v>
       </c>
       <c r="C81">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D81">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>maca.mariotti</v>
+        <v>odeivisoncardoso</v>
       </c>
       <c r="B82">
         <v>1</v>
       </c>
       <c r="C82">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D82">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>adriano.trator</v>
+        <v>maca.mariotti</v>
       </c>
       <c r="B83">
         <v>1</v>
       </c>
       <c r="C83">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D83">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>s__simone__</v>
+        <v>adriano.trator</v>
       </c>
       <c r="B84">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C84">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="D84">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>kaua_limaofc</v>
+        <v>s__simone__</v>
       </c>
       <c r="B85">
         <v>2</v>
@@ -1592,7 +1592,7 @@
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>clouddhidden</v>
+        <v>kaua_limaofc</v>
       </c>
       <c r="B86">
         <v>2</v>
@@ -1606,21 +1606,21 @@
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>lucascardosol__</v>
+        <v>clouddhidden</v>
       </c>
       <c r="B87">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C87">
         <v>0</v>
       </c>
       <c r="D87">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>ruangzk</v>
+        <v>lucascardosol__</v>
       </c>
       <c r="B88">
         <v>1</v>
@@ -1634,41 +1634,41 @@
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>washington_cassisno</v>
+        <v>ruangzk</v>
       </c>
       <c r="B89">
         <v>1</v>
       </c>
       <c r="C89">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D89">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>ismaeldaniell</v>
+        <v>livreseseguras</v>
       </c>
       <c r="B90">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C90">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D90">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>douglasipvr_mma</v>
+        <v>washington_cassisno</v>
       </c>
       <c r="B91">
         <v>1</v>
       </c>
       <c r="C91">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D91">
         <v>2</v>
@@ -1676,13 +1676,13 @@
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>tassiogiloficial</v>
+        <v>ismaeldaniell</v>
       </c>
       <c r="B92">
         <v>2</v>
       </c>
       <c r="C92">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D92">
         <v>0</v>
@@ -1690,21 +1690,21 @@
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>vnciuss__df</v>
+        <v>douglasipvr_mma</v>
       </c>
       <c r="B93">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C93">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D93">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>jhee_dias</v>
+        <v>tassiogiloficial</v>
       </c>
       <c r="B94">
         <v>2</v>
@@ -1718,49 +1718,49 @@
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>albertoleandromoco</v>
+        <v>vnciuss__df</v>
       </c>
       <c r="B95">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C95">
         <v>2</v>
       </c>
       <c r="D95">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>pauloserrati</v>
+        <v>jhee_dias</v>
       </c>
       <c r="B96">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C96">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D96">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>jhonatas_ricardo</v>
+        <v>albertoleandromoco</v>
       </c>
       <c r="B97">
         <v>1</v>
       </c>
       <c r="C97">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D97">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>fredoctmma</v>
+        <v>pauloserrati</v>
       </c>
       <c r="B98">
         <v>1</v>
@@ -1769,26 +1769,26 @@
         <v>1</v>
       </c>
       <c r="D98">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>diegopaivajj</v>
+        <v>jhonatas_ricardo</v>
       </c>
       <c r="B99">
         <v>1</v>
       </c>
       <c r="C99">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D99">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>fabaotipster</v>
+        <v>fredoctmma</v>
       </c>
       <c r="B100">
         <v>1</v>
@@ -1802,35 +1802,35 @@
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>joegam3r</v>
+        <v>diegopaivajj</v>
       </c>
       <c r="B101">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C101">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D101">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="str">
-        <v>mimuniz.bjj</v>
+        <v>fabaotipster</v>
       </c>
       <c r="B102">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C102">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D102">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="str">
-        <v>orafao1</v>
+        <v>joegam3r</v>
       </c>
       <c r="B103">
         <v>2</v>
@@ -1844,7 +1844,7 @@
     </row>
     <row r="104">
       <c r="A104" t="str">
-        <v>fabi.godooy</v>
+        <v>mimuniz.bjj</v>
       </c>
       <c r="B104">
         <v>2</v>
@@ -1858,35 +1858,35 @@
     </row>
     <row r="105">
       <c r="A105" t="str">
-        <v>leobahiamma</v>
+        <v>orafao1</v>
       </c>
       <c r="B105">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C105">
         <v>0</v>
       </c>
       <c r="D105">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="str">
-        <v>marcosmeireles_pqd_</v>
+        <v>fabi.godooy</v>
       </c>
       <c r="B106">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C106">
         <v>0</v>
       </c>
       <c r="D106">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="str">
-        <v>gabriel.junior20bjj</v>
+        <v>leobahiamma</v>
       </c>
       <c r="B107">
         <v>1</v>
@@ -1900,7 +1900,7 @@
     </row>
     <row r="108">
       <c r="A108" t="str">
-        <v>heltoncm2002</v>
+        <v>marcosmeireles_pqd_</v>
       </c>
       <c r="B108">
         <v>1</v>
@@ -1914,7 +1914,7 @@
     </row>
     <row r="109">
       <c r="A109" t="str">
-        <v>raelduraes</v>
+        <v>gabriel.junior20bjj</v>
       </c>
       <c r="B109">
         <v>1</v>
@@ -1928,7 +1928,7 @@
     </row>
     <row r="110">
       <c r="A110" t="str">
-        <v>fernando.nogueira.7792</v>
+        <v>heltoncm2002</v>
       </c>
       <c r="B110">
         <v>1</v>
@@ -1942,7 +1942,7 @@
     </row>
     <row r="111">
       <c r="A111" t="str">
-        <v>mineirinho_jj</v>
+        <v>raelduraes</v>
       </c>
       <c r="B111">
         <v>1</v>
@@ -1956,7 +1956,7 @@
     </row>
     <row r="112">
       <c r="A112" t="str">
-        <v>graalino</v>
+        <v>fernando.nogueira.7792</v>
       </c>
       <c r="B112">
         <v>1</v>
@@ -1970,7 +1970,7 @@
     </row>
     <row r="113">
       <c r="A113" t="str">
-        <v>lopesbrunao</v>
+        <v>mineirinho_jj</v>
       </c>
       <c r="B113">
         <v>1</v>
@@ -1984,7 +1984,7 @@
     </row>
     <row r="114">
       <c r="A114" t="str">
-        <v>pedrinhosbjj</v>
+        <v>graalino</v>
       </c>
       <c r="B114">
         <v>1</v>
@@ -1998,35 +1998,35 @@
     </row>
     <row r="115">
       <c r="A115" t="str">
-        <v>treinaadorrafael</v>
+        <v>lopesbrunao</v>
       </c>
       <c r="B115">
         <v>1</v>
       </c>
       <c r="C115">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D115">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="str">
-        <v>benjafloripabjj</v>
+        <v>pedrinhosbjj</v>
       </c>
       <c r="B116">
         <v>1</v>
       </c>
       <c r="C116">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D116">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="str">
-        <v>fernando.mma</v>
+        <v>treinaadorrafael</v>
       </c>
       <c r="B117">
         <v>1</v>
@@ -2040,7 +2040,7 @@
     </row>
     <row r="118">
       <c r="A118" t="str">
-        <v>dr.daniloduartefisio</v>
+        <v>benjafloripabjj</v>
       </c>
       <c r="B118">
         <v>1</v>
@@ -2054,13 +2054,13 @@
     </row>
     <row r="119">
       <c r="A119" t="str">
-        <v>diegosilvabjjoficial</v>
+        <v>fernando.mma</v>
       </c>
       <c r="B119">
         <v>1</v>
       </c>
       <c r="C119">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D119">
         <v>0</v>
@@ -2068,13 +2068,13 @@
     </row>
     <row r="120">
       <c r="A120" t="str">
-        <v>fagnerosensei</v>
+        <v>dr.daniloduartefisio</v>
       </c>
       <c r="B120">
         <v>1</v>
       </c>
       <c r="C120">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D120">
         <v>0</v>
@@ -2082,13 +2082,13 @@
     </row>
     <row r="121">
       <c r="A121" t="str">
-        <v>030sami</v>
+        <v>diegosilvabjjoficial</v>
       </c>
       <c r="B121">
         <v>1</v>
       </c>
       <c r="C121">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D121">
         <v>0</v>
@@ -2096,21 +2096,21 @@
     </row>
     <row r="122">
       <c r="A122" t="str">
-        <v>luanlacerda_ufc_61kg</v>
+        <v>fagnerosensei</v>
       </c>
       <c r="B122">
         <v>1</v>
       </c>
       <c r="C122">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D122">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="str">
-        <v>guiiviieira_</v>
+        <v>030sami</v>
       </c>
       <c r="B123">
         <v>1</v>
@@ -2124,21 +2124,21 @@
     </row>
     <row r="124">
       <c r="A124" t="str">
-        <v>cshigueo</v>
+        <v>luanlacerda_ufc_61kg</v>
       </c>
       <c r="B124">
         <v>1</v>
       </c>
       <c r="C124">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D124">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="str">
-        <v>vitorhugo_vtr</v>
+        <v>guiiviieira_</v>
       </c>
       <c r="B125">
         <v>1</v>
@@ -2152,7 +2152,7 @@
     </row>
     <row r="126">
       <c r="A126" t="str">
-        <v>emerson_lucaszx</v>
+        <v>cshigueo</v>
       </c>
       <c r="B126">
         <v>1</v>
@@ -2166,7 +2166,7 @@
     </row>
     <row r="127">
       <c r="A127" t="str">
-        <v>danni_goncalves12</v>
+        <v>vitorhugo_vtr</v>
       </c>
       <c r="B127">
         <v>1</v>
@@ -2180,7 +2180,7 @@
     </row>
     <row r="128">
       <c r="A128" t="str">
-        <v>mttsm._</v>
+        <v>emerson_lucaszx</v>
       </c>
       <c r="B128">
         <v>1</v>
@@ -2194,7 +2194,7 @@
     </row>
     <row r="129">
       <c r="A129" t="str">
-        <v>andrealvess02</v>
+        <v>danni_goncalves12</v>
       </c>
       <c r="B129">
         <v>1</v>
@@ -2208,7 +2208,7 @@
     </row>
     <row r="130">
       <c r="A130" t="str">
-        <v>gildojiu</v>
+        <v>mttsm._</v>
       </c>
       <c r="B130">
         <v>1</v>
@@ -2222,7 +2222,7 @@
     </row>
     <row r="131">
       <c r="A131" t="str">
-        <v>kawannsennast</v>
+        <v>andrealvess02</v>
       </c>
       <c r="B131">
         <v>1</v>
@@ -2236,7 +2236,7 @@
     </row>
     <row r="132">
       <c r="A132" t="str">
-        <v>yurimartins1_</v>
+        <v>gildojiu</v>
       </c>
       <c r="B132">
         <v>1</v>
@@ -2250,7 +2250,7 @@
     </row>
     <row r="133">
       <c r="A133" t="str">
-        <v>matheusteodoro_1</v>
+        <v>kawannsennast</v>
       </c>
       <c r="B133">
         <v>1</v>
@@ -2264,7 +2264,7 @@
     </row>
     <row r="134">
       <c r="A134" t="str">
-        <v>maria.pereiradeoliveira.5283</v>
+        <v>yurimartins1_</v>
       </c>
       <c r="B134">
         <v>1</v>
@@ -2278,13 +2278,13 @@
     </row>
     <row r="135">
       <c r="A135" t="str">
-        <v>kael_lyto</v>
+        <v>matheusteodoro_1</v>
       </c>
       <c r="B135">
         <v>1</v>
       </c>
       <c r="C135">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D135">
         <v>0</v>
@@ -2292,27 +2292,27 @@
     </row>
     <row r="136">
       <c r="A136" t="str">
-        <v>cristianpsicologo</v>
+        <v>maria.pereiradeoliveira.5283</v>
       </c>
       <c r="B136">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C136">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="D136">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="str">
-        <v>juanx.pontes</v>
+        <v>kael_lyto</v>
       </c>
       <c r="B137">
         <v>1</v>
       </c>
       <c r="C137">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D137">
         <v>0</v>
@@ -2320,13 +2320,13 @@
     </row>
     <row r="138">
       <c r="A138" t="str">
-        <v>select_from_joao</v>
+        <v>kalindrafaria</v>
       </c>
       <c r="B138">
         <v>1</v>
       </c>
       <c r="C138">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D138">
         <v>0</v>
@@ -2334,21 +2334,21 @@
     </row>
     <row r="139">
       <c r="A139" t="str">
-        <v>yeslifeacademia</v>
+        <v>cristianpsicologo</v>
       </c>
       <c r="B139">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C139">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D139">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="str">
-        <v>ojaimerocha</v>
+        <v>juanx.pontes</v>
       </c>
       <c r="B140">
         <v>1</v>
@@ -2362,13 +2362,13 @@
     </row>
     <row r="141">
       <c r="A141" t="str">
-        <v>tonketjudes</v>
+        <v>select_from_joao</v>
       </c>
       <c r="B141">
         <v>1</v>
       </c>
       <c r="C141">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D141">
         <v>0</v>
@@ -2376,13 +2376,13 @@
     </row>
     <row r="142">
       <c r="A142" t="str">
-        <v>_eliasffx</v>
+        <v>yeslifeacademia</v>
       </c>
       <c r="B142">
         <v>1</v>
       </c>
       <c r="C142">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D142">
         <v>0</v>
@@ -2390,13 +2390,13 @@
     </row>
     <row r="143">
       <c r="A143" t="str">
-        <v>pdfiv</v>
+        <v>ojaimerocha</v>
       </c>
       <c r="B143">
         <v>1</v>
       </c>
       <c r="C143">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D143">
         <v>0</v>
@@ -2404,7 +2404,7 @@
     </row>
     <row r="144">
       <c r="A144" t="str">
-        <v>mariaraimundad940</v>
+        <v>tonketjudes</v>
       </c>
       <c r="B144">
         <v>1</v>
@@ -2418,7 +2418,7 @@
     </row>
     <row r="145">
       <c r="A145" t="str">
-        <v>gabesantos.13</v>
+        <v>_eliasffx</v>
       </c>
       <c r="B145">
         <v>1</v>
@@ -2432,7 +2432,7 @@
     </row>
     <row r="146">
       <c r="A146" t="str">
-        <v>euvitormirandaa</v>
+        <v>pdfiv</v>
       </c>
       <c r="B146">
         <v>1</v>
@@ -2446,7 +2446,7 @@
     </row>
     <row r="147">
       <c r="A147" t="str">
-        <v>thompsonborralho</v>
+        <v>mariaraimundad940</v>
       </c>
       <c r="B147">
         <v>1</v>
@@ -2460,7 +2460,7 @@
     </row>
     <row r="148">
       <c r="A148" t="str">
-        <v>frankikolimabjj</v>
+        <v>gabesantos.13</v>
       </c>
       <c r="B148">
         <v>1</v>
@@ -2474,7 +2474,7 @@
     </row>
     <row r="149">
       <c r="A149" t="str">
-        <v>alerrandrojj</v>
+        <v>euvitormirandaa</v>
       </c>
       <c r="B149">
         <v>1</v>
@@ -2488,7 +2488,7 @@
     </row>
     <row r="150">
       <c r="A150" t="str">
-        <v>anahangelica</v>
+        <v>thompsonborralho</v>
       </c>
       <c r="B150">
         <v>1</v>
@@ -2502,7 +2502,7 @@
     </row>
     <row r="151">
       <c r="A151" t="str">
-        <v>teacherthalesyouplus</v>
+        <v>frankikolimabjj</v>
       </c>
       <c r="B151">
         <v>1</v>
@@ -2516,7 +2516,7 @@
     </row>
     <row r="152">
       <c r="A152" t="str">
-        <v>minotaurinho</v>
+        <v>alerrandrojj</v>
       </c>
       <c r="B152">
         <v>1</v>
@@ -2530,7 +2530,7 @@
     </row>
     <row r="153">
       <c r="A153" t="str">
-        <v>lara.rpr</v>
+        <v>anahangelica</v>
       </c>
       <c r="B153">
         <v>1</v>
@@ -2544,7 +2544,7 @@
     </row>
     <row r="154">
       <c r="A154" t="str">
-        <v>codasqueves</v>
+        <v>teacherthalesyouplus</v>
       </c>
       <c r="B154">
         <v>1</v>
@@ -2558,7 +2558,7 @@
     </row>
     <row r="155">
       <c r="A155" t="str">
-        <v>yan_touro.7766</v>
+        <v>minotaurinho</v>
       </c>
       <c r="B155">
         <v>1</v>
@@ -2572,7 +2572,7 @@
     </row>
     <row r="156">
       <c r="A156" t="str">
-        <v>carolinne.xwp</v>
+        <v>lara.rpr</v>
       </c>
       <c r="B156">
         <v>1</v>
@@ -2586,7 +2586,7 @@
     </row>
     <row r="157">
       <c r="A157" t="str">
-        <v>davicorbella</v>
+        <v>codasqueves</v>
       </c>
       <c r="B157">
         <v>1</v>
@@ -2600,7 +2600,7 @@
     </row>
     <row r="158">
       <c r="A158" t="str">
-        <v>isaac.bah_starinazzo</v>
+        <v>yan_touro.7766</v>
       </c>
       <c r="B158">
         <v>1</v>
@@ -2614,7 +2614,7 @@
     </row>
     <row r="159">
       <c r="A159" t="str">
-        <v>cjrnavalhaoficial</v>
+        <v>carolinne.xwp</v>
       </c>
       <c r="B159">
         <v>1</v>
@@ -2628,7 +2628,7 @@
     </row>
     <row r="160">
       <c r="A160" t="str">
-        <v>artemio_bjj</v>
+        <v>davicorbella</v>
       </c>
       <c r="B160">
         <v>1</v>
@@ -2642,7 +2642,7 @@
     </row>
     <row r="161">
       <c r="A161" t="str">
-        <v>katiaecarreraf</v>
+        <v>isaac.bah_starinazzo</v>
       </c>
       <c r="B161">
         <v>1</v>
@@ -2656,7 +2656,7 @@
     </row>
     <row r="162">
       <c r="A162" t="str">
-        <v>geraldocnetomma</v>
+        <v>cjrnavalhaoficial</v>
       </c>
       <c r="B162">
         <v>1</v>
@@ -2670,21 +2670,21 @@
     </row>
     <row r="163">
       <c r="A163" t="str">
-        <v>pedro_pavin_</v>
+        <v>artemio_bjj</v>
       </c>
       <c r="B163">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C163">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D163">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="str">
-        <v>xavyeroficial</v>
+        <v>katiaecarreraf</v>
       </c>
       <c r="B164">
         <v>1</v>
@@ -2698,7 +2698,7 @@
     </row>
     <row r="165">
       <c r="A165" t="str">
-        <v>maryanagandra</v>
+        <v>geraldocnetomma</v>
       </c>
       <c r="B165">
         <v>1</v>
@@ -2712,21 +2712,21 @@
     </row>
     <row r="166">
       <c r="A166" t="str">
-        <v>eliandropires</v>
+        <v>pedro_pavin_</v>
       </c>
       <c r="B166">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C166">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D166">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="str">
-        <v>charlesanthony2466</v>
+        <v>xavyeroficial</v>
       </c>
       <c r="B167">
         <v>1</v>
@@ -2740,7 +2740,7 @@
     </row>
     <row r="168">
       <c r="A168" t="str">
-        <v>guga.llisboa_bjj</v>
+        <v>maryanagandra</v>
       </c>
       <c r="B168">
         <v>1</v>
@@ -2754,7 +2754,7 @@
     </row>
     <row r="169">
       <c r="A169" t="str">
-        <v>draanapaulaponceano</v>
+        <v>eliandropires</v>
       </c>
       <c r="B169">
         <v>1</v>
@@ -2768,7 +2768,7 @@
     </row>
     <row r="170">
       <c r="A170" t="str">
-        <v>saj_photo_miami</v>
+        <v>charlesanthony2466</v>
       </c>
       <c r="B170">
         <v>1</v>
@@ -2782,7 +2782,7 @@
     </row>
     <row r="171">
       <c r="A171" t="str">
-        <v>alternativaremocoes</v>
+        <v>guga.llisboa_bjj</v>
       </c>
       <c r="B171">
         <v>1</v>
@@ -2796,7 +2796,7 @@
     </row>
     <row r="172">
       <c r="A172" t="str">
-        <v>benivalentinn</v>
+        <v>draanapaulaponceano</v>
       </c>
       <c r="B172">
         <v>1</v>
@@ -2810,7 +2810,7 @@
     </row>
     <row r="173">
       <c r="A173" t="str">
-        <v>miguelrodriguesbjj</v>
+        <v>saj_photo_miami</v>
       </c>
       <c r="B173">
         <v>1</v>
@@ -2824,7 +2824,7 @@
     </row>
     <row r="174">
       <c r="A174" t="str">
-        <v>navarro_9430</v>
+        <v>alternativaremocoes</v>
       </c>
       <c r="B174">
         <v>1</v>
@@ -2838,7 +2838,7 @@
     </row>
     <row r="175">
       <c r="A175" t="str">
-        <v>_puroosso88</v>
+        <v>benivalentinn</v>
       </c>
       <c r="B175">
         <v>1</v>
@@ -2852,7 +2852,7 @@
     </row>
     <row r="176">
       <c r="A176" t="str">
-        <v>_rayysp</v>
+        <v>miguelrodriguesbjj</v>
       </c>
       <c r="B176">
         <v>1</v>
@@ -2866,7 +2866,7 @@
     </row>
     <row r="177">
       <c r="A177" t="str">
-        <v>cami.terra_</v>
+        <v>navarro_9430</v>
       </c>
       <c r="B177">
         <v>1</v>
@@ -2880,7 +2880,7 @@
     </row>
     <row r="178">
       <c r="A178" t="str">
-        <v>gabicardoson</v>
+        <v>_puroosso88</v>
       </c>
       <c r="B178">
         <v>1</v>
@@ -2894,7 +2894,7 @@
     </row>
     <row r="179">
       <c r="A179" t="str">
-        <v>martta.mariah</v>
+        <v>_rayysp</v>
       </c>
       <c r="B179">
         <v>1</v>
@@ -2908,7 +2908,7 @@
     </row>
     <row r="180">
       <c r="A180" t="str">
-        <v>wlt_miguel</v>
+        <v>cami.terra_</v>
       </c>
       <c r="B180">
         <v>1</v>
@@ -2922,7 +2922,7 @@
     </row>
     <row r="181">
       <c r="A181" t="str">
-        <v>jaonevesz</v>
+        <v>gabicardoson</v>
       </c>
       <c r="B181">
         <v>1</v>
@@ -2936,7 +2936,7 @@
     </row>
     <row r="182">
       <c r="A182" t="str">
-        <v>pietroshz</v>
+        <v>martta.mariah</v>
       </c>
       <c r="B182">
         <v>1</v>
@@ -2950,7 +2950,7 @@
     </row>
     <row r="183">
       <c r="A183" t="str">
-        <v>___neller</v>
+        <v>wlt_miguel</v>
       </c>
       <c r="B183">
         <v>1</v>
@@ -2964,7 +2964,7 @@
     </row>
     <row r="184">
       <c r="A184" t="str">
-        <v>_bety_marcal</v>
+        <v>jaonevesz</v>
       </c>
       <c r="B184">
         <v>1</v>
@@ -2978,7 +2978,7 @@
     </row>
     <row r="185">
       <c r="A185" t="str">
-        <v>guilhermeefelix__</v>
+        <v>pietroshz</v>
       </c>
       <c r="B185">
         <v>1</v>
@@ -2992,7 +2992,7 @@
     </row>
     <row r="186">
       <c r="A186" t="str">
-        <v>pativinisf</v>
+        <v>___neller</v>
       </c>
       <c r="B186">
         <v>1</v>
@@ -3006,7 +3006,7 @@
     </row>
     <row r="187">
       <c r="A187" t="str">
-        <v>judadany</v>
+        <v>_bety_marcal</v>
       </c>
       <c r="B187">
         <v>1</v>
@@ -3020,7 +3020,7 @@
     </row>
     <row r="188">
       <c r="A188" t="str">
-        <v>andre_alcausa</v>
+        <v>guilhermeefelix__</v>
       </c>
       <c r="B188">
         <v>1</v>
@@ -3034,7 +3034,7 @@
     </row>
     <row r="189">
       <c r="A189" t="str">
-        <v>_fernunes</v>
+        <v>pativinisf</v>
       </c>
       <c r="B189">
         <v>1</v>
@@ -3048,7 +3048,7 @@
     </row>
     <row r="190">
       <c r="A190" t="str">
-        <v>aloirmarcal</v>
+        <v>judadany</v>
       </c>
       <c r="B190">
         <v>1</v>
@@ -3062,7 +3062,7 @@
     </row>
     <row r="191">
       <c r="A191" t="str">
-        <v>gilberto_7606</v>
+        <v>andre_alcausa</v>
       </c>
       <c r="B191">
         <v>1</v>
@@ -3076,7 +3076,7 @@
     </row>
     <row r="192">
       <c r="A192" t="str">
-        <v>edinalvajanjacomo</v>
+        <v>_fernunes</v>
       </c>
       <c r="B192">
         <v>1</v>
@@ -3090,7 +3090,7 @@
     </row>
     <row r="193">
       <c r="A193" t="str">
-        <v>flazuera14</v>
+        <v>aloirmarcal</v>
       </c>
       <c r="B193">
         <v>1</v>
@@ -3104,7 +3104,7 @@
     </row>
     <row r="194">
       <c r="A194" t="str">
-        <v>wilson_n_janjacomo</v>
+        <v>gilberto_7606</v>
       </c>
       <c r="B194">
         <v>1</v>
@@ -3118,7 +3118,7 @@
     </row>
     <row r="195">
       <c r="A195" t="str">
-        <v>camii_bonfim</v>
+        <v>edinalvajanjacomo</v>
       </c>
       <c r="B195">
         <v>1</v>
@@ -3132,7 +3132,7 @@
     </row>
     <row r="196">
       <c r="A196" t="str">
-        <v>danlouiz.jj</v>
+        <v>flazuera14</v>
       </c>
       <c r="B196">
         <v>1</v>
@@ -3146,7 +3146,7 @@
     </row>
     <row r="197">
       <c r="A197" t="str">
-        <v>gabriel_trevelin</v>
+        <v>wilson_n_janjacomo</v>
       </c>
       <c r="B197">
         <v>1</v>
@@ -3160,7 +3160,7 @@
     </row>
     <row r="198">
       <c r="A198" t="str">
-        <v>y.arthur_01</v>
+        <v>camii_bonfim</v>
       </c>
       <c r="B198">
         <v>1</v>
@@ -3174,7 +3174,7 @@
     </row>
     <row r="199">
       <c r="A199" t="str">
-        <v>muricunha</v>
+        <v>danlouiz.jj</v>
       </c>
       <c r="B199">
         <v>1</v>
@@ -3188,7 +3188,7 @@
     </row>
     <row r="200">
       <c r="A200" t="str">
-        <v>victorhenriquebjj</v>
+        <v>gabriel_trevelin</v>
       </c>
       <c r="B200">
         <v>1</v>
@@ -3202,7 +3202,7 @@
     </row>
     <row r="201">
       <c r="A201" t="str">
-        <v>_lsanchess_</v>
+        <v>y.arthur_01</v>
       </c>
       <c r="B201">
         <v>1</v>
@@ -3216,7 +3216,7 @@
     </row>
     <row r="202">
       <c r="A202" t="str">
-        <v>__bielgg</v>
+        <v>muricunha</v>
       </c>
       <c r="B202">
         <v>1</v>
@@ -3230,7 +3230,7 @@
     </row>
     <row r="203">
       <c r="A203" t="str">
-        <v>mr__rlk01</v>
+        <v>victorhenriquebjj</v>
       </c>
       <c r="B203">
         <v>1</v>
@@ -3244,7 +3244,7 @@
     </row>
     <row r="204">
       <c r="A204" t="str">
-        <v>vitor_buck</v>
+        <v>_lsanchess_</v>
       </c>
       <c r="B204">
         <v>1</v>
@@ -3258,7 +3258,7 @@
     </row>
     <row r="205">
       <c r="A205" t="str">
-        <v>fran.ruys</v>
+        <v>__bielgg</v>
       </c>
       <c r="B205">
         <v>1</v>
@@ -3272,7 +3272,7 @@
     </row>
     <row r="206">
       <c r="A206" t="str">
-        <v>arthurhenrique.sx</v>
+        <v>mr__rlk01</v>
       </c>
       <c r="B206">
         <v>1</v>
@@ -3286,7 +3286,7 @@
     </row>
     <row r="207">
       <c r="A207" t="str">
-        <v>wesley_bjjvc</v>
+        <v>vitor_buck</v>
       </c>
       <c r="B207">
         <v>1</v>
@@ -3300,7 +3300,7 @@
     </row>
     <row r="208">
       <c r="A208" t="str">
-        <v>sambagabrieloficial</v>
+        <v>fran.ruys</v>
       </c>
       <c r="B208">
         <v>1</v>
@@ -3314,7 +3314,7 @@
     </row>
     <row r="209">
       <c r="A209" t="str">
-        <v>peacegrappler</v>
+        <v>arthurhenrique.sx</v>
       </c>
       <c r="B209">
         <v>1</v>
@@ -3328,7 +3328,7 @@
     </row>
     <row r="210">
       <c r="A210" t="str">
-        <v>aliferpaulo_</v>
+        <v>wesley_bjjvc</v>
       </c>
       <c r="B210">
         <v>1</v>
@@ -3342,7 +3342,7 @@
     </row>
     <row r="211">
       <c r="A211" t="str">
-        <v>_alcantara.bru</v>
+        <v>sambagabrieloficial</v>
       </c>
       <c r="B211">
         <v>1</v>
@@ -3356,7 +3356,7 @@
     </row>
     <row r="212">
       <c r="A212" t="str">
-        <v>cesar.boanerges</v>
+        <v>peacegrappler</v>
       </c>
       <c r="B212">
         <v>1</v>
@@ -3370,7 +3370,7 @@
     </row>
     <row r="213">
       <c r="A213" t="str">
-        <v>cezary_oleksiejczuk</v>
+        <v>aliferpaulo_</v>
       </c>
       <c r="B213">
         <v>1</v>
@@ -3384,7 +3384,7 @@
     </row>
     <row r="214">
       <c r="A214" t="str">
-        <v>alexandreconsentino</v>
+        <v>_alcantara.bru</v>
       </c>
       <c r="B214">
         <v>1</v>
@@ -3398,7 +3398,7 @@
     </row>
     <row r="215">
       <c r="A215" t="str">
-        <v>erivan_sousa_tico</v>
+        <v>cesar.boanerges</v>
       </c>
       <c r="B215">
         <v>1</v>
@@ -3412,13 +3412,13 @@
     </row>
     <row r="216">
       <c r="A216" t="str">
-        <v>rafaela_duaartee</v>
+        <v>cezary_oleksiejczuk</v>
       </c>
       <c r="B216">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C216">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="D216">
         <v>0</v>
@@ -3426,7 +3426,7 @@
     </row>
     <row r="217">
       <c r="A217" t="str">
-        <v>wagner_alexandre_w_a</v>
+        <v>alexandreconsentino</v>
       </c>
       <c r="B217">
         <v>1</v>
@@ -3440,7 +3440,7 @@
     </row>
     <row r="218">
       <c r="A218" t="str">
-        <v>andre.legendre.10</v>
+        <v>erivan_sousa_tico</v>
       </c>
       <c r="B218">
         <v>1</v>
@@ -3454,13 +3454,13 @@
     </row>
     <row r="219">
       <c r="A219" t="str">
-        <v>phillipe.harry</v>
+        <v>rafaela_duaartee</v>
       </c>
       <c r="B219">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C219">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D219">
         <v>0</v>
@@ -3468,7 +3468,7 @@
     </row>
     <row r="220">
       <c r="A220" t="str">
-        <v>andrejetx</v>
+        <v>wagner_alexandre_w_a</v>
       </c>
       <c r="B220">
         <v>1</v>
@@ -3482,7 +3482,7 @@
     </row>
     <row r="221">
       <c r="A221" t="str">
-        <v>leandro_motiv4</v>
+        <v>andre.legendre.10</v>
       </c>
       <c r="B221">
         <v>1</v>
@@ -3496,7 +3496,7 @@
     </row>
     <row r="222">
       <c r="A222" t="str">
-        <v>olga.oliveira013</v>
+        <v>phillipe.harry</v>
       </c>
       <c r="B222">
         <v>1</v>
@@ -3510,7 +3510,7 @@
     </row>
     <row r="223">
       <c r="A223" t="str">
-        <v>vinyrodriguesoficial</v>
+        <v>andrejetx</v>
       </c>
       <c r="B223">
         <v>1</v>
@@ -3524,7 +3524,7 @@
     </row>
     <row r="224">
       <c r="A224" t="str">
-        <v>leosacraa</v>
+        <v>leandro_motiv4</v>
       </c>
       <c r="B224">
         <v>1</v>
@@ -3538,7 +3538,7 @@
     </row>
     <row r="225">
       <c r="A225" t="str">
-        <v>gutocriativo</v>
+        <v>olga.oliveira013</v>
       </c>
       <c r="B225">
         <v>1</v>
@@ -3552,7 +3552,7 @@
     </row>
     <row r="226">
       <c r="A226" t="str">
-        <v>igorfso_</v>
+        <v>vinyrodriguesoficial</v>
       </c>
       <c r="B226">
         <v>1</v>
@@ -3566,7 +3566,7 @@
     </row>
     <row r="227">
       <c r="A227" t="str">
-        <v>gabrielsilva_mma</v>
+        <v>leosacraa</v>
       </c>
       <c r="B227">
         <v>1</v>
@@ -3580,7 +3580,7 @@
     </row>
     <row r="228">
       <c r="A228" t="str">
-        <v>lay_roqs</v>
+        <v>gutocriativo</v>
       </c>
       <c r="B228">
         <v>1</v>
@@ -3594,7 +3594,7 @@
     </row>
     <row r="229">
       <c r="A229" t="str">
-        <v>bigjota.artist</v>
+        <v>igorfso_</v>
       </c>
       <c r="B229">
         <v>1</v>
@@ -3608,7 +3608,7 @@
     </row>
     <row r="230">
       <c r="A230" t="str">
-        <v>jhoninhaoficial031</v>
+        <v>gabrielsilva_mma</v>
       </c>
       <c r="B230">
         <v>1</v>
@@ -3622,7 +3622,7 @@
     </row>
     <row r="231">
       <c r="A231" t="str">
-        <v>mth_fernandes031</v>
+        <v>lay_roqs</v>
       </c>
       <c r="B231">
         <v>1</v>
@@ -3636,7 +3636,7 @@
     </row>
     <row r="232">
       <c r="A232" t="str">
-        <v>drfelipeoliveira_adv</v>
+        <v>bigjota.artist</v>
       </c>
       <c r="B232">
         <v>1</v>
@@ -3650,7 +3650,7 @@
     </row>
     <row r="233">
       <c r="A233" t="str">
-        <v>turmanmma</v>
+        <v>jhoninhaoficial031</v>
       </c>
       <c r="B233">
         <v>1</v>
@@ -3664,7 +3664,7 @@
     </row>
     <row r="234">
       <c r="A234" t="str">
-        <v>gustavomohallem</v>
+        <v>mth_fernandes031</v>
       </c>
       <c r="B234">
         <v>1</v>
@@ -3678,13 +3678,13 @@
     </row>
     <row r="235">
       <c r="A235" t="str">
-        <v>marinealcausa</v>
+        <v>drfelipeoliveira_adv</v>
       </c>
       <c r="B235">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C235">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="D235">
         <v>0</v>
@@ -3692,13 +3692,13 @@
     </row>
     <row r="236">
       <c r="A236" t="str">
-        <v>emersonriosmma</v>
+        <v>turmanmma</v>
       </c>
       <c r="B236">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C236">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="D236">
         <v>0</v>
@@ -3706,41 +3706,41 @@
     </row>
     <row r="237">
       <c r="A237" t="str">
-        <v>luizcosta_mma</v>
+        <v>gustavomohallem</v>
       </c>
       <c r="B237">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C237">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D237">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="str">
-        <v>giulia.fasolato</v>
+        <v>atlta.marc0s</v>
       </c>
       <c r="B238">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C238">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D238">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="str">
-        <v>michelle_mirele</v>
+        <v>arturbambam</v>
       </c>
       <c r="B239">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C239">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D239">
         <v>0</v>
@@ -3748,13 +3748,13 @@
     </row>
     <row r="240">
       <c r="A240" t="str">
-        <v>danielfranzesilva</v>
+        <v>marinealcausa</v>
       </c>
       <c r="B240">
         <v>0</v>
       </c>
       <c r="C240">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D240">
         <v>0</v>
@@ -3762,21 +3762,21 @@
     </row>
     <row r="241">
       <c r="A241" t="str">
-        <v>ednilsonkaicai</v>
+        <v>emersonriosmma</v>
       </c>
       <c r="B241">
         <v>0</v>
       </c>
       <c r="C241">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D241">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="str">
-        <v>sirleneferreiradiasdias</v>
+        <v>luizcosta_mma</v>
       </c>
       <c r="B242">
         <v>0</v>
@@ -3785,12 +3785,12 @@
         <v>2</v>
       </c>
       <c r="D242">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="str">
-        <v>dayanaa1511</v>
+        <v>giulia.fasolato</v>
       </c>
       <c r="B243">
         <v>0</v>
@@ -3799,46 +3799,46 @@
         <v>2</v>
       </c>
       <c r="D243">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="str">
-        <v>vanessamelomma</v>
+        <v>michelle_mirele</v>
       </c>
       <c r="B244">
         <v>0</v>
       </c>
       <c r="C244">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D244">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="str">
-        <v>leonardopateira</v>
+        <v>danielfranzesilva</v>
       </c>
       <c r="B245">
         <v>0</v>
       </c>
       <c r="C245">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D245">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="str">
-        <v>rahikikhalid</v>
+        <v>ednilsonkaicai</v>
       </c>
       <c r="B246">
         <v>0</v>
       </c>
       <c r="C246">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D246">
         <v>1</v>
@@ -3846,7 +3846,7 @@
     </row>
     <row r="247">
       <c r="A247" t="str">
-        <v>manumito.oficial</v>
+        <v>sirleneferreiradiasdias</v>
       </c>
       <c r="B247">
         <v>0</v>
@@ -3855,12 +3855,12 @@
         <v>2</v>
       </c>
       <c r="D247">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="str">
-        <v>carlosnoelblack</v>
+        <v>dayanaa1511</v>
       </c>
       <c r="B248">
         <v>0</v>
@@ -3869,26 +3869,26 @@
         <v>2</v>
       </c>
       <c r="D248">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="str">
-        <v>jhonnatanboxe_</v>
+        <v>vanessamelomma</v>
       </c>
       <c r="B249">
         <v>0</v>
       </c>
       <c r="C249">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D249">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="str">
-        <v>lokomemo_protetores</v>
+        <v>leonardopateira</v>
       </c>
       <c r="B250">
         <v>0</v>
@@ -3902,7 +3902,7 @@
     </row>
     <row r="251">
       <c r="A251" t="str">
-        <v>coutz11</v>
+        <v>rahikikhalid</v>
       </c>
       <c r="B251">
         <v>0</v>
@@ -3916,7 +3916,7 @@
     </row>
     <row r="252">
       <c r="A252" t="str">
-        <v>orlando_alfa09</v>
+        <v>manumito.oficial</v>
       </c>
       <c r="B252">
         <v>0</v>
@@ -3930,7 +3930,7 @@
     </row>
     <row r="253">
       <c r="A253" t="str">
-        <v>vitorshowman</v>
+        <v>carlosnoelblack</v>
       </c>
       <c r="B253">
         <v>0</v>
@@ -3944,7 +3944,7 @@
     </row>
     <row r="254">
       <c r="A254" t="str">
-        <v>4lissson</v>
+        <v>jhonnatanboxe_</v>
       </c>
       <c r="B254">
         <v>0</v>
@@ -3958,7 +3958,7 @@
     </row>
     <row r="255">
       <c r="A255" t="str">
-        <v>danilofernandescf</v>
+        <v>lokomemo_protetores</v>
       </c>
       <c r="B255">
         <v>0</v>
@@ -3972,7 +3972,7 @@
     </row>
     <row r="256">
       <c r="A256" t="str">
-        <v>bryandazuera</v>
+        <v>coutz11</v>
       </c>
       <c r="B256">
         <v>0</v>
@@ -3986,49 +3986,49 @@
     </row>
     <row r="257">
       <c r="A257" t="str">
-        <v>ommariotti</v>
+        <v>orlando_alfa09</v>
       </c>
       <c r="B257">
         <v>0</v>
       </c>
       <c r="C257">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D257">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="str">
-        <v>brodschack_</v>
+        <v>vitorshowman</v>
       </c>
       <c r="B258">
         <v>0</v>
       </c>
       <c r="C258">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D258">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="str">
-        <v>_vpft</v>
+        <v>4lissson</v>
       </c>
       <c r="B259">
         <v>0</v>
       </c>
       <c r="C259">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D259">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="str">
-        <v>mariacleusa.lopes</v>
+        <v>danilofernandescf</v>
       </c>
       <c r="B260">
         <v>0</v>
@@ -4037,12 +4037,12 @@
         <v>1</v>
       </c>
       <c r="D260">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="str">
-        <v>helenaseveribjj</v>
+        <v>bryandazuera</v>
       </c>
       <c r="B261">
         <v>0</v>
@@ -4051,12 +4051,12 @@
         <v>1</v>
       </c>
       <c r="D261">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="str">
-        <v>_kainanlima</v>
+        <v>ommariotti</v>
       </c>
       <c r="B262">
         <v>0</v>
@@ -4065,12 +4065,12 @@
         <v>1</v>
       </c>
       <c r="D262">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="str">
-        <v>jimmy_indioap</v>
+        <v>brodschack_</v>
       </c>
       <c r="B263">
         <v>0</v>
@@ -4079,12 +4079,12 @@
         <v>1</v>
       </c>
       <c r="D263">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="str">
-        <v>omar_alneaimi</v>
+        <v>_vpft</v>
       </c>
       <c r="B264">
         <v>0</v>
@@ -4093,12 +4093,12 @@
         <v>1</v>
       </c>
       <c r="D264">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="str">
-        <v>victor_brunopersonal</v>
+        <v>mariacleusa.lopes</v>
       </c>
       <c r="B265">
         <v>0</v>
@@ -4112,7 +4112,7 @@
     </row>
     <row r="266">
       <c r="A266" t="str">
-        <v>motumbo_team</v>
+        <v>helenaseveribjj</v>
       </c>
       <c r="B266">
         <v>0</v>
@@ -4126,7 +4126,7 @@
     </row>
     <row r="267">
       <c r="A267" t="str">
-        <v>vanemessina</v>
+        <v>_kainanlima</v>
       </c>
       <c r="B267">
         <v>0</v>
@@ -4140,7 +4140,7 @@
     </row>
     <row r="268">
       <c r="A268" t="str">
-        <v>dadwillians</v>
+        <v>jimmy_indioap</v>
       </c>
       <c r="B268">
         <v>0</v>
@@ -4154,7 +4154,7 @@
     </row>
     <row r="269">
       <c r="A269" t="str">
-        <v>thalytabjj</v>
+        <v>omar_alneaimi</v>
       </c>
       <c r="B269">
         <v>0</v>
@@ -4168,7 +4168,7 @@
     </row>
     <row r="270">
       <c r="A270" t="str">
-        <v>flavio.dequeiroz</v>
+        <v>victor_brunopersonal</v>
       </c>
       <c r="B270">
         <v>0</v>
@@ -4182,7 +4182,7 @@
     </row>
     <row r="271">
       <c r="A271" t="str">
-        <v>esteticaluharruda</v>
+        <v>motumbo_team</v>
       </c>
       <c r="B271">
         <v>0</v>
@@ -4196,7 +4196,7 @@
     </row>
     <row r="272">
       <c r="A272" t="str">
-        <v>chubotaru_lilu</v>
+        <v>vanemessina</v>
       </c>
       <c r="B272">
         <v>0</v>
@@ -4210,7 +4210,7 @@
     </row>
     <row r="273">
       <c r="A273" t="str">
-        <v>eusoufernandosaito</v>
+        <v>dadwillians</v>
       </c>
       <c r="B273">
         <v>0</v>
@@ -4224,7 +4224,7 @@
     </row>
     <row r="274">
       <c r="A274" t="str">
-        <v>dandraco_</v>
+        <v>thalytabjj</v>
       </c>
       <c r="B274">
         <v>0</v>
@@ -4238,7 +4238,7 @@
     </row>
     <row r="275">
       <c r="A275" t="str">
-        <v>oliveiraandiarabjj</v>
+        <v>flavio.dequeiroz</v>
       </c>
       <c r="B275">
         <v>0</v>
@@ -4252,7 +4252,7 @@
     </row>
     <row r="276">
       <c r="A276" t="str">
-        <v>sejamotivadorofc</v>
+        <v>esteticaluharruda</v>
       </c>
       <c r="B276">
         <v>0</v>
@@ -4266,7 +4266,7 @@
     </row>
     <row r="277">
       <c r="A277" t="str">
-        <v>tpapereira</v>
+        <v>chubotaru_lilu</v>
       </c>
       <c r="B277">
         <v>0</v>
@@ -4280,7 +4280,7 @@
     </row>
     <row r="278">
       <c r="A278" t="str">
-        <v>kfcampeoes</v>
+        <v>eusoufernandosaito</v>
       </c>
       <c r="B278">
         <v>0</v>
@@ -4294,7 +4294,7 @@
     </row>
     <row r="279">
       <c r="A279" t="str">
-        <v>herrickmarinho</v>
+        <v>dandraco_</v>
       </c>
       <c r="B279">
         <v>0</v>
@@ -4308,7 +4308,7 @@
     </row>
     <row r="280">
       <c r="A280" t="str">
-        <v>rafaelcmjj</v>
+        <v>oliveiraandiarabjj</v>
       </c>
       <c r="B280">
         <v>0</v>
@@ -4322,7 +4322,7 @@
     </row>
     <row r="281">
       <c r="A281" t="str">
-        <v>cristianomarcello</v>
+        <v>sejamotivadorofc</v>
       </c>
       <c r="B281">
         <v>0</v>
@@ -4336,7 +4336,7 @@
     </row>
     <row r="282">
       <c r="A282" t="str">
-        <v>_gabrielpego</v>
+        <v>tpapereira</v>
       </c>
       <c r="B282">
         <v>0</v>
@@ -4350,7 +4350,7 @@
     </row>
     <row r="283">
       <c r="A283" t="str">
-        <v>taylor_71kg</v>
+        <v>kfcampeoes</v>
       </c>
       <c r="B283">
         <v>0</v>
@@ -4364,7 +4364,7 @@
     </row>
     <row r="284">
       <c r="A284" t="str">
-        <v>marcilio.silva.71404</v>
+        <v>herrickmarinho</v>
       </c>
       <c r="B284">
         <v>0</v>
@@ -4378,7 +4378,7 @@
     </row>
     <row r="285">
       <c r="A285" t="str">
-        <v>doraasivla</v>
+        <v>rafaelcmjj</v>
       </c>
       <c r="B285">
         <v>0</v>
@@ -4392,7 +4392,7 @@
     </row>
     <row r="286">
       <c r="A286" t="str">
-        <v>pe.mirandas</v>
+        <v>cristianomarcello</v>
       </c>
       <c r="B286">
         <v>0</v>
@@ -4406,7 +4406,7 @@
     </row>
     <row r="287">
       <c r="A287" t="str">
-        <v>leaoanaalice</v>
+        <v>_gabrielpego</v>
       </c>
       <c r="B287">
         <v>0</v>
@@ -4420,7 +4420,7 @@
     </row>
     <row r="288">
       <c r="A288" t="str">
-        <v>caioparangole</v>
+        <v>taylor_71kg</v>
       </c>
       <c r="B288">
         <v>0</v>
@@ -4434,7 +4434,7 @@
     </row>
     <row r="289">
       <c r="A289" t="str">
-        <v>sabrinaalsilva</v>
+        <v>marcilio.silva.71404</v>
       </c>
       <c r="B289">
         <v>0</v>
@@ -4448,7 +4448,7 @@
     </row>
     <row r="290">
       <c r="A290" t="str">
-        <v>nuncadesistir.nd</v>
+        <v>doraasivla</v>
       </c>
       <c r="B290">
         <v>0</v>
@@ -4462,7 +4462,7 @@
     </row>
     <row r="291">
       <c r="A291" t="str">
-        <v>eglaudiomma</v>
+        <v>pe.mirandas</v>
       </c>
       <c r="B291">
         <v>0</v>
@@ -4476,7 +4476,7 @@
     </row>
     <row r="292">
       <c r="A292" t="str">
-        <v>strong_stg_oficial</v>
+        <v>leaoanaalice</v>
       </c>
       <c r="B292">
         <v>0</v>
@@ -4490,7 +4490,7 @@
     </row>
     <row r="293">
       <c r="A293" t="str">
-        <v>ricardotofanello</v>
+        <v>caioparangole</v>
       </c>
       <c r="B293">
         <v>0</v>
@@ -4504,7 +4504,7 @@
     </row>
     <row r="294">
       <c r="A294" t="str">
-        <v>taporondebruno</v>
+        <v>sabrinaalsilva</v>
       </c>
       <c r="B294">
         <v>0</v>
@@ -4518,7 +4518,7 @@
     </row>
     <row r="295">
       <c r="A295" t="str">
-        <v>anamatias.m</v>
+        <v>nuncadesistir.nd</v>
       </c>
       <c r="B295">
         <v>0</v>
@@ -4532,7 +4532,7 @@
     </row>
     <row r="296">
       <c r="A296" t="str">
-        <v>claudio_marchese_7</v>
+        <v>eglaudiomma</v>
       </c>
       <c r="B296">
         <v>0</v>
@@ -4546,7 +4546,7 @@
     </row>
     <row r="297">
       <c r="A297" t="str">
-        <v>1000ton_n</v>
+        <v>strong_stg_oficial</v>
       </c>
       <c r="B297">
         <v>0</v>
@@ -4560,7 +4560,7 @@
     </row>
     <row r="298">
       <c r="A298" t="str">
-        <v>paulo.titoo</v>
+        <v>ricardotofanello</v>
       </c>
       <c r="B298">
         <v>0</v>
@@ -4574,7 +4574,7 @@
     </row>
     <row r="299">
       <c r="A299" t="str">
-        <v>vitorcosta_mma</v>
+        <v>taporondebruno</v>
       </c>
       <c r="B299">
         <v>0</v>
@@ -4588,7 +4588,7 @@
     </row>
     <row r="300">
       <c r="A300" t="str">
-        <v>couragemma</v>
+        <v>anamatias.m</v>
       </c>
       <c r="B300">
         <v>0</v>
@@ -4602,7 +4602,7 @@
     </row>
     <row r="301">
       <c r="A301" t="str">
-        <v>romulerasilva</v>
+        <v>claudio_marchese_7</v>
       </c>
       <c r="B301">
         <v>0</v>
@@ -4616,7 +4616,7 @@
     </row>
     <row r="302">
       <c r="A302" t="str">
-        <v>edergama.mma</v>
+        <v>1000ton_n</v>
       </c>
       <c r="B302">
         <v>0</v>
@@ -4630,7 +4630,7 @@
     </row>
     <row r="303">
       <c r="A303" t="str">
-        <v>alineanne_</v>
+        <v>paulo.titoo</v>
       </c>
       <c r="B303">
         <v>0</v>
@@ -4644,7 +4644,7 @@
     </row>
     <row r="304">
       <c r="A304" t="str">
-        <v>julckreis</v>
+        <v>vitorcosta_mma</v>
       </c>
       <c r="B304">
         <v>0</v>
@@ -4658,7 +4658,7 @@
     </row>
     <row r="305">
       <c r="A305" t="str">
-        <v>andreza.thais.1</v>
+        <v>couragemma</v>
       </c>
       <c r="B305">
         <v>0</v>
@@ -4672,7 +4672,7 @@
     </row>
     <row r="306">
       <c r="A306" t="str">
-        <v>benicius_edu</v>
+        <v>romulerasilva</v>
       </c>
       <c r="B306">
         <v>0</v>
@@ -4686,7 +4686,7 @@
     </row>
     <row r="307">
       <c r="A307" t="str">
-        <v>nataliaemanuela.personal</v>
+        <v>edergama.mma</v>
       </c>
       <c r="B307">
         <v>0</v>
@@ -4700,7 +4700,7 @@
     </row>
     <row r="308">
       <c r="A308" t="str">
-        <v>michele_mixa</v>
+        <v>alineanne_</v>
       </c>
       <c r="B308">
         <v>0</v>
@@ -4714,7 +4714,7 @@
     </row>
     <row r="309">
       <c r="A309" t="str">
-        <v>joaolauar_</v>
+        <v>julckreis</v>
       </c>
       <c r="B309">
         <v>0</v>
@@ -4728,7 +4728,7 @@
     </row>
     <row r="310">
       <c r="A310" t="str">
-        <v>igorbrasileiro01</v>
+        <v>andreza.thais.1</v>
       </c>
       <c r="B310">
         <v>0</v>
@@ -4742,7 +4742,7 @@
     </row>
     <row r="311">
       <c r="A311" t="str">
-        <v>felipeocalmon</v>
+        <v>benicius_edu</v>
       </c>
       <c r="B311">
         <v>0</v>
@@ -4756,7 +4756,7 @@
     </row>
     <row r="312">
       <c r="A312" t="str">
-        <v>rejr_mma</v>
+        <v>nataliaemanuela.personal</v>
       </c>
       <c r="B312">
         <v>0</v>
@@ -4770,7 +4770,7 @@
     </row>
     <row r="313">
       <c r="A313" t="str">
-        <v>deivssonmanin</v>
+        <v>michele_mixa</v>
       </c>
       <c r="B313">
         <v>0</v>
@@ -4784,7 +4784,7 @@
     </row>
     <row r="314">
       <c r="A314" t="str">
-        <v>andrey_m_s_</v>
+        <v>joaolauar_</v>
       </c>
       <c r="B314">
         <v>0</v>
@@ -4798,7 +4798,7 @@
     </row>
     <row r="315">
       <c r="A315" t="str">
-        <v>vidaldanin</v>
+        <v>igorbrasileiro01</v>
       </c>
       <c r="B315">
         <v>0</v>
@@ -4812,7 +4812,7 @@
     </row>
     <row r="316">
       <c r="A316" t="str">
-        <v>barbaracontadora</v>
+        <v>felipeocalmon</v>
       </c>
       <c r="B316">
         <v>0</v>
@@ -4826,7 +4826,7 @@
     </row>
     <row r="317">
       <c r="A317" t="str">
-        <v>natalves5</v>
+        <v>rejr_mma</v>
       </c>
       <c r="B317">
         <v>0</v>
@@ -4840,7 +4840,7 @@
     </row>
     <row r="318">
       <c r="A318" t="str">
-        <v>marlon_bodybuilding</v>
+        <v>deivssonmanin</v>
       </c>
       <c r="B318">
         <v>0</v>
@@ -4854,7 +4854,7 @@
     </row>
     <row r="319">
       <c r="A319" t="str">
-        <v>boradepodcastoficial</v>
+        <v>andrey_m_s_</v>
       </c>
       <c r="B319">
         <v>0</v>
@@ -4868,7 +4868,7 @@
     </row>
     <row r="320">
       <c r="A320" t="str">
-        <v>audizioandrade</v>
+        <v>vidaldanin</v>
       </c>
       <c r="B320">
         <v>0</v>
@@ -4882,7 +4882,7 @@
     </row>
     <row r="321">
       <c r="A321" t="str">
-        <v>isadoragolimpio</v>
+        <v>barbaracontadora</v>
       </c>
       <c r="B321">
         <v>0</v>
@@ -4896,7 +4896,7 @@
     </row>
     <row r="322">
       <c r="A322" t="str">
-        <v>dudu.acabamentos</v>
+        <v>natalves5</v>
       </c>
       <c r="B322">
         <v>0</v>
@@ -4910,7 +4910,7 @@
     </row>
     <row r="323">
       <c r="A323" t="str">
-        <v>katlembrenda</v>
+        <v>marlon_bodybuilding</v>
       </c>
       <c r="B323">
         <v>0</v>
@@ -4924,7 +4924,7 @@
     </row>
     <row r="324">
       <c r="A324" t="str">
-        <v>aline.amaral21</v>
+        <v>boradepodcastoficial</v>
       </c>
       <c r="B324">
         <v>0</v>
@@ -4938,7 +4938,7 @@
     </row>
     <row r="325">
       <c r="A325" t="str">
-        <v>tamysregina</v>
+        <v>audizioandrade</v>
       </c>
       <c r="B325">
         <v>0</v>
@@ -4952,7 +4952,7 @@
     </row>
     <row r="326">
       <c r="A326" t="str">
-        <v>guilhermews1994</v>
+        <v>isadoragolimpio</v>
       </c>
       <c r="B326">
         <v>0</v>
@@ -4966,7 +4966,7 @@
     </row>
     <row r="327">
       <c r="A327" t="str">
-        <v>percepcar</v>
+        <v>dudu.acabamentos</v>
       </c>
       <c r="B327">
         <v>0</v>
@@ -4980,7 +4980,7 @@
     </row>
     <row r="328">
       <c r="A328" t="str">
-        <v>kevin.mota95</v>
+        <v>katlembrenda</v>
       </c>
       <c r="B328">
         <v>0</v>
@@ -4994,7 +4994,7 @@
     </row>
     <row r="329">
       <c r="A329" t="str">
-        <v>_marcos_.71</v>
+        <v>aline.amaral21</v>
       </c>
       <c r="B329">
         <v>0</v>
@@ -5008,7 +5008,7 @@
     </row>
     <row r="330">
       <c r="A330" t="str">
-        <v>douglas_vitor8</v>
+        <v>tamysregina</v>
       </c>
       <c r="B330">
         <v>0</v>
@@ -5022,7 +5022,7 @@
     </row>
     <row r="331">
       <c r="A331" t="str">
-        <v>gemeaslauraebrenda</v>
+        <v>guilhermews1994</v>
       </c>
       <c r="B331">
         <v>0</v>
@@ -5036,7 +5036,7 @@
     </row>
     <row r="332">
       <c r="A332" t="str">
-        <v>raulcarvalho1010</v>
+        <v>percepcar</v>
       </c>
       <c r="B332">
         <v>0</v>
@@ -5050,7 +5050,7 @@
     </row>
     <row r="333">
       <c r="A333" t="str">
-        <v>roginbrito</v>
+        <v>kevin.mota95</v>
       </c>
       <c r="B333">
         <v>0</v>
@@ -5064,7 +5064,7 @@
     </row>
     <row r="334">
       <c r="A334" t="str">
-        <v>meirelesmma</v>
+        <v>_marcos_.71</v>
       </c>
       <c r="B334">
         <v>0</v>
@@ -5078,7 +5078,7 @@
     </row>
     <row r="335">
       <c r="A335" t="str">
-        <v>dvlucc2k26_</v>
+        <v>douglas_vitor8</v>
       </c>
       <c r="B335">
         <v>0</v>
@@ -5092,28 +5092,140 @@
     </row>
     <row r="336">
       <c r="A336" t="str">
+        <v>gemeaslauraebrenda</v>
+      </c>
+      <c r="B336">
+        <v>0</v>
+      </c>
+      <c r="C336">
+        <v>1</v>
+      </c>
+      <c r="D336">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="337">
+      <c r="A337" t="str">
+        <v>raulcarvalho1010</v>
+      </c>
+      <c r="B337">
+        <v>0</v>
+      </c>
+      <c r="C337">
+        <v>1</v>
+      </c>
+      <c r="D337">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="338">
+      <c r="A338" t="str">
+        <v>roginbrito</v>
+      </c>
+      <c r="B338">
+        <v>0</v>
+      </c>
+      <c r="C338">
+        <v>1</v>
+      </c>
+      <c r="D338">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="339">
+      <c r="A339" t="str">
+        <v>meirelesmma</v>
+      </c>
+      <c r="B339">
+        <v>0</v>
+      </c>
+      <c r="C339">
+        <v>1</v>
+      </c>
+      <c r="D339">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="340">
+      <c r="A340" t="str">
+        <v>dvlucc2k26_</v>
+      </c>
+      <c r="B340">
+        <v>0</v>
+      </c>
+      <c r="C340">
+        <v>1</v>
+      </c>
+      <c r="D340">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="341">
+      <c r="A341" t="str">
         <v>armysenju</v>
       </c>
-      <c r="B336">
-        <v>0</v>
-      </c>
-      <c r="C336">
-        <v>1</v>
-      </c>
-      <c r="D336">
+      <c r="B341">
+        <v>0</v>
+      </c>
+      <c r="C341">
+        <v>1</v>
+      </c>
+      <c r="D341">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="342">
+      <c r="A342" t="str">
+        <v>f.ostini</v>
+      </c>
+      <c r="B342">
+        <v>0</v>
+      </c>
+      <c r="C342">
+        <v>1</v>
+      </c>
+      <c r="D342">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="343">
+      <c r="A343" t="str">
+        <v>fher.nando_</v>
+      </c>
+      <c r="B343">
+        <v>0</v>
+      </c>
+      <c r="C343">
+        <v>1</v>
+      </c>
+      <c r="D343">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="344">
+      <c r="A344" t="str">
+        <v>cristiannogueira.vtt</v>
+      </c>
+      <c r="B344">
+        <v>0</v>
+      </c>
+      <c r="C344">
+        <v>1</v>
+      </c>
+      <c r="D344">
         <v>0</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D336"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D344"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D30"/>
+  <dimension ref="A1:D43"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -5134,13 +5246,13 @@
         <v>peacegrappler_mma</v>
       </c>
       <c r="B2">
-        <v>198</v>
+        <v>268</v>
       </c>
       <c r="C2">
         <v>0</v>
       </c>
       <c r="D2">
-        <v>194</v>
+        <v>263</v>
       </c>
     </row>
     <row r="3">
@@ -5148,7 +5260,7 @@
         <v>hugo7jj</v>
       </c>
       <c r="B3">
-        <v>54</v>
+        <v>66</v>
       </c>
       <c r="C3">
         <v>0</v>
@@ -5159,30 +5271,30 @@
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>rm.nicki</v>
+        <v>enzocardoso.bjj</v>
       </c>
       <c r="B4">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="C4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D4">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>enzocardoso.bjj</v>
+        <v>rm.nicki</v>
       </c>
       <c r="B5">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="C5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D5">
-        <v>29</v>
+        <v>37</v>
       </c>
     </row>
     <row r="6">
@@ -5190,10 +5302,10 @@
         <v>rpsantos_mma</v>
       </c>
       <c r="B6">
-        <v>31</v>
+        <v>45</v>
       </c>
       <c r="C6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D6">
         <v>23</v>
@@ -5204,80 +5316,80 @@
         <v>pablofiorindi</v>
       </c>
       <c r="B7">
-        <v>25</v>
+        <v>37</v>
       </c>
       <c r="C7">
         <v>0</v>
       </c>
       <c r="D7">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>quemuel_ottoni</v>
+        <v>pedr00jj</v>
       </c>
       <c r="B8">
+        <v>29</v>
+      </c>
+      <c r="C8">
+        <v>0</v>
+      </c>
+      <c r="D8">
         <v>17</v>
-      </c>
-      <c r="C8">
-        <v>4</v>
-      </c>
-      <c r="D8">
-        <v>19</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>pedr00jj</v>
+        <v>quemuel_ottoni</v>
       </c>
       <c r="B9">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="C9">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D9">
-        <v>13</v>
+        <v>20</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>anaaj_camargo</v>
+        <v>luis_pequeno_mma</v>
       </c>
       <c r="B10">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C10">
         <v>0</v>
       </c>
       <c r="D10">
-        <v>9</v>
+        <v>13</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>pg_grappling</v>
+        <v>anaaj_camargo</v>
       </c>
       <c r="B11">
+        <v>12</v>
+      </c>
+      <c r="C11">
+        <v>0</v>
+      </c>
+      <c r="D11">
         <v>9</v>
-      </c>
-      <c r="C11">
-        <v>0</v>
-      </c>
-      <c r="D11">
-        <v>7</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>cleyton_jesuss</v>
+        <v>pg_grappling</v>
       </c>
       <c r="B12">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="C12">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D12">
         <v>7</v>
@@ -5285,16 +5397,16 @@
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>luis_pequeno_mma</v>
+        <v>cleyton_jesuss</v>
       </c>
       <c r="B13">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="C13">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D13">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="14">
@@ -5305,18 +5417,18 @@
         <v>3</v>
       </c>
       <c r="C14">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D14">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>_beegomes_</v>
+        <v>aline.r15</v>
       </c>
       <c r="B15">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C15">
         <v>0</v>
@@ -5327,7 +5439,7 @@
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>karen.ottoni</v>
+        <v>irmandadefightteam</v>
       </c>
       <c r="B16">
         <v>2</v>
@@ -5341,7 +5453,7 @@
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>alfredo_miras</v>
+        <v>excelentfightcompetition</v>
       </c>
       <c r="B17">
         <v>2</v>
@@ -5355,10 +5467,10 @@
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>mmmarc20</v>
+        <v>_beegomes_</v>
       </c>
       <c r="B18">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C18">
         <v>0</v>
@@ -5369,7 +5481,7 @@
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>badboykillermma</v>
+        <v>karen.ottoni</v>
       </c>
       <c r="B19">
         <v>2</v>
@@ -5383,7 +5495,7 @@
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>gra_jpereira</v>
+        <v>alfredo_miras</v>
       </c>
       <c r="B20">
         <v>2</v>
@@ -5397,7 +5509,7 @@
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>ninjatheorist</v>
+        <v>mmmarc20</v>
       </c>
       <c r="B21">
         <v>2</v>
@@ -5411,66 +5523,66 @@
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>god.motivacao</v>
+        <v>badboykillermma</v>
       </c>
       <c r="B22">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C22">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="D22">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>ronemayanmorais</v>
+        <v>gra_jpereira</v>
       </c>
       <c r="B23">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C23">
         <v>0</v>
       </c>
       <c r="D23">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>maxgandra</v>
+        <v>ninjatheorist</v>
       </c>
       <c r="B24">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C24">
         <v>0</v>
       </c>
       <c r="D24">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>pedrinhosbjj</v>
+        <v>god.motivacao</v>
       </c>
       <c r="B25">
         <v>1</v>
       </c>
       <c r="C25">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="D25">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>combintel</v>
+        <v>maxgandra</v>
       </c>
       <c r="B26">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C26">
         <v>0</v>
@@ -5481,7 +5593,7 @@
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>enzoferrari680</v>
+        <v>livreseseguras</v>
       </c>
       <c r="B27">
         <v>1</v>
@@ -5490,12 +5602,12 @@
         <v>0</v>
       </c>
       <c r="D27">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>gustavomohallem</v>
+        <v>ronemayanmorais</v>
       </c>
       <c r="B28">
         <v>1</v>
@@ -5504,18 +5616,18 @@
         <v>0</v>
       </c>
       <c r="D28">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>tabajaraharu</v>
+        <v>pedrinhosbjj</v>
       </c>
       <c r="B29">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C29">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D29">
         <v>1</v>
@@ -5523,21 +5635,203 @@
     </row>
     <row r="30">
       <c r="A30" t="str">
+        <v>combintel</v>
+      </c>
+      <c r="B30">
+        <v>1</v>
+      </c>
+      <c r="C30">
+        <v>0</v>
+      </c>
+      <c r="D30">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="str">
+        <v>pedromadeira.s</v>
+      </c>
+      <c r="B31">
+        <v>1</v>
+      </c>
+      <c r="C31">
+        <v>0</v>
+      </c>
+      <c r="D31">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="str">
+        <v>kalindrafaria</v>
+      </c>
+      <c r="B32">
+        <v>1</v>
+      </c>
+      <c r="C32">
+        <v>0</v>
+      </c>
+      <c r="D32">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="str">
+        <v>enzoferrari680</v>
+      </c>
+      <c r="B33">
+        <v>1</v>
+      </c>
+      <c r="C33">
+        <v>0</v>
+      </c>
+      <c r="D33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="str">
+        <v>gustavomohallem</v>
+      </c>
+      <c r="B34">
+        <v>1</v>
+      </c>
+      <c r="C34">
+        <v>0</v>
+      </c>
+      <c r="D34">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="str">
+        <v>atlta.marc0s</v>
+      </c>
+      <c r="B35">
+        <v>1</v>
+      </c>
+      <c r="C35">
+        <v>0</v>
+      </c>
+      <c r="D35">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="str">
+        <v>arturbambam</v>
+      </c>
+      <c r="B36">
+        <v>1</v>
+      </c>
+      <c r="C36">
+        <v>0</v>
+      </c>
+      <c r="D36">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="str">
+        <v>tabajaraharu</v>
+      </c>
+      <c r="B37">
+        <v>0</v>
+      </c>
+      <c r="C37">
+        <v>1</v>
+      </c>
+      <c r="D37">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="str">
+        <v>eliassilverio</v>
+      </c>
+      <c r="B38">
+        <v>0</v>
+      </c>
+      <c r="C38">
+        <v>1</v>
+      </c>
+      <c r="D38">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="str">
         <v>benjafloripabjj</v>
       </c>
-      <c r="B30">
-        <v>0</v>
-      </c>
-      <c r="C30">
-        <v>1</v>
-      </c>
-      <c r="D30">
+      <c r="B39">
+        <v>0</v>
+      </c>
+      <c r="C39">
+        <v>1</v>
+      </c>
+      <c r="D39">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="str">
+        <v>f.ostini</v>
+      </c>
+      <c r="B40">
+        <v>0</v>
+      </c>
+      <c r="C40">
+        <v>1</v>
+      </c>
+      <c r="D40">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="str">
+        <v>marcos_tailandess</v>
+      </c>
+      <c r="B41">
+        <v>0</v>
+      </c>
+      <c r="C41">
+        <v>1</v>
+      </c>
+      <c r="D41">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="str">
+        <v>fher.nando_</v>
+      </c>
+      <c r="B42">
+        <v>0</v>
+      </c>
+      <c r="C42">
+        <v>1</v>
+      </c>
+      <c r="D42">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="str">
+        <v>cristiannogueira.vtt</v>
+      </c>
+      <c r="B43">
+        <v>0</v>
+      </c>
+      <c r="C43">
+        <v>1</v>
+      </c>
+      <c r="D43">
         <v>0</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D30"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D43"/>
   </ignoredErrors>
 </worksheet>
 </file>